--- a/BUOI06.xlsx
+++ b/BUOI06.xlsx
@@ -5,21 +5,32 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Huyen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thanh Huyen\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA506E9C-265B-4867-A947-1DCBC2AD69B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17FCDCB8-683E-4993-88E4-A8E6D2D54F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{A466A881-85F9-4517-B725-8187DF326750}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="6" xr2:uid="{A466A881-85F9-4517-B725-8187DF326750}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="2a" sheetId="4" r:id="rId1"/>
+    <sheet name="2b" sheetId="5" r:id="rId2"/>
+    <sheet name="2c" sheetId="6" r:id="rId3"/>
+    <sheet name="2d" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Sheet1!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Sheet2!$A$1:$C$1</definedName>
+    <definedName name="Query_from_Excel_Files" localSheetId="0" hidden="1">'2a'!$A$1:$D$2</definedName>
+    <definedName name="Query_from_Excel_Files" localSheetId="1" hidden="1">'2b'!$A$1:$E$5</definedName>
+    <definedName name="Query_from_Excel_Files" localSheetId="2" hidden="1">'2c'!$A$1:$E$2</definedName>
+    <definedName name="Query_from_Excel_Files" localSheetId="3" hidden="1">'2d'!$A$1:$F$2</definedName>
+    <definedName name="sheet1">Sheet1!$A$1:$D$15</definedName>
+    <definedName name="sheet2">Sheet2!$A$1:$C$15</definedName>
+    <definedName name="sheet3">Sheet3!$A$1:$C$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,8 +50,25 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{BB56BABB-42C4-4380-BBDD-7F4AC7202825}" name="Query from Excel Files" type="1" refreshedVersion="8" background="1" saveData="1">
+    <dbPr connection="DSN=Excel Files;DBQ=D:\BUOI06 - Copy.xlsx;DefaultDir=D:\;DriverId=1046;MaxBufferSize=2048;PageTimeout=5;" command="SELECT `Sheet1$`.MSSV, `Sheet1$`.Hoten, `Sheet1$`.F3, `Sheet1$`.Lop_x000d__x000a_FROM `D:\BUOI06 - Copy.xlsx`.`Sheet1$` `Sheet1$`_x000d__x000a_WHERE (`Sheet1$`.Lop='DI1296A1') OR (`Sheet1$`.Lop='DI1296A2')"/>
+  </connection>
+  <connection id="2" xr16:uid="{FC599676-6B4D-42E0-BAD9-F21A27CBD319}" name="Query from Excel Files1" type="1" refreshedVersion="8" background="1" saveData="1">
+    <dbPr connection="DSN=Excel Files;DBQ=D:\BUOI06 - Copy.xlsx;DefaultDir=D:\;DriverId=1046;MaxBufferSize=2048;PageTimeout=5;" command="SELECT Sheet1.MSSV, Sheet1.Hoten, Sheet1.F3, Sheet1.Lop, Sheet2.MaMH_x000d__x000a_FROM `Sheet1$` Sheet1 _x000d__x000a_INNER JOIN `Sheet2$` Sheet2 _x000d__x000a_   ON Sheet1.MSSV = Sheet2.MSSV_x000d__x000a_WHERE Sheet2.MaMH = 'CT178'"/>
+  </connection>
+  <connection id="3" xr16:uid="{EEB3EED0-B84F-4E97-8605-C9B2B245B066}" name="Query from Excel Files2" type="1" refreshedVersion="8" background="1" saveData="1">
+    <dbPr connection="DSN=Excel Files;DBQ=D:\BUOI06 - Copy.xlsx;DefaultDir=D:\;DriverId=1046;MaxBufferSize=2048;PageTimeout=5;" command="SELECT Sheet1.MSSV, Sheet1.Hoten, Sheet1.F3, Sheet1.Lop, Sheet2.MaMH_x000d__x000a_FROM `Sheet1$` Sheet1 _x000d__x000a_INNER JOIN `Sheet2$` Sheet2 _x000d__x000a_   ON Sheet1.MSSV = Sheet2.MSSV_x000d__x000a_WHERE Sheet1.Lop = 'CP1296C1' _x000d__x000a_  AND Sheet2.MaMH = 'CT178'"/>
+  </connection>
+  <connection id="4" xr16:uid="{07202ABD-4515-4E70-BA5D-D04A92BE6A08}" name="Query from Excel Files3" type="1" refreshedVersion="8" background="1" saveData="1">
+    <dbPr connection="DSN=Excel Files;DBQ=D:\BUOI06 - Copy.xlsx;DefaultDir=D:\;DriverId=1046;MaxBufferSize=2048;PageTimeout=5;" command="SELECT Sheet1.MSSV, Sheet1.Hoten, Sheet1.F3, Sheet1.Lop, Sheet2.MaMH, Sheet2.Diem_x000d__x000a_FROM `Sheet1$` Sheet1 _x000d__x000a_INNER JOIN `Sheet2$` Sheet2 _x000d__x000a_   ON Sheet1.MSSV = Sheet2.MSSV_x000d__x000a_WHERE Sheet1.Lop = 'CP1296C1' _x000d__x000a_  AND Sheet2.MaMH = 'CT178' _x000d__x000a_  AND Sheet2.Diem = 'C'"/>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="67">
   <si>
     <t>MSSV</t>
   </si>
@@ -238,13 +266,16 @@
   </si>
   <si>
     <t>Nen tang CNTT</t>
+  </si>
+  <si>
+    <t>F3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +305,13 @@
       <family val="1"/>
       <charset val="163"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="163"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -283,7 +321,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -399,39 +437,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -457,41 +472,351 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="21">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="163"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -502,6 +827,118 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="Query from Excel Files" connectionId="1" xr16:uid="{6A5581DF-F2C8-416B-BA8D-F5694DF52C7E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="5">
+    <queryTableFields count="4">
+      <queryTableField id="1" name="MSSV" tableColumnId="1"/>
+      <queryTableField id="2" name="Hoten" tableColumnId="2"/>
+      <queryTableField id="3" name="F3" tableColumnId="3"/>
+      <queryTableField id="4" name="Lop" tableColumnId="4"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="Query from Excel Files" connectionId="2" xr16:uid="{4B7B1737-E4F9-416C-995D-23A8B79F6539}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="6">
+    <queryTableFields count="5">
+      <queryTableField id="1" name="MSSV" tableColumnId="1"/>
+      <queryTableField id="2" name="Hoten" tableColumnId="2"/>
+      <queryTableField id="3" name="F3" tableColumnId="3"/>
+      <queryTableField id="4" name="Lop" tableColumnId="4"/>
+      <queryTableField id="5" name="MaMH" tableColumnId="5"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="Query from Excel Files" connectionId="3" xr16:uid="{525D6AAD-ECBC-4EC5-8EC4-86B65CBC2BB4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="6">
+    <queryTableFields count="5">
+      <queryTableField id="1" name="MSSV" tableColumnId="1"/>
+      <queryTableField id="2" name="Hoten" tableColumnId="2"/>
+      <queryTableField id="3" name="F3" tableColumnId="3"/>
+      <queryTableField id="4" name="Lop" tableColumnId="4"/>
+      <queryTableField id="5" name="MaMH" tableColumnId="5"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="Query from Excel Files" connectionId="4" xr16:uid="{928D7FD8-2CD9-4B60-97A5-974205C98100}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
+  <queryTableRefresh nextId="7">
+    <queryTableFields count="6">
+      <queryTableField id="1" name="MSSV" tableColumnId="1"/>
+      <queryTableField id="2" name="Hoten" tableColumnId="2"/>
+      <queryTableField id="3" name="F3" tableColumnId="3"/>
+      <queryTableField id="4" name="Lop" tableColumnId="4"/>
+      <queryTableField id="5" name="MaMH" tableColumnId="5"/>
+      <queryTableField id="6" name="Diem" tableColumnId="6"/>
+    </queryTableFields>
+  </queryTableRefresh>
+</queryTable>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D864EAD8-2BB7-452D-AD51-CDD046E1246B}" name="Table_Query_from_Excel_Files" displayName="Table_Query_from_Excel_Files" ref="A1:D2" tableType="queryTable" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A1:D2" xr:uid="{D864EAD8-2BB7-452D-AD51-CDD046E1246B}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{6ACFE18D-C883-4E25-B944-52616FE834E1}" uniqueName="1" name="MSSV" queryTableFieldId="1" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{241AA8EF-96B2-4E5A-B929-95F772AAD3D0}" uniqueName="2" name="Hoten" queryTableFieldId="2" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{E92E1377-87F9-4A01-A8E9-E2B715B68C60}" uniqueName="3" name="F3" queryTableFieldId="3" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{574102E8-ED16-4435-99D9-0EB0CD448043}" uniqueName="4" name="Lop" queryTableFieldId="4" dataDxfId="17"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{ABC29F28-E7B5-4281-A032-714C1CF765FF}" name="Table_Query_from_Excel_Files3" displayName="Table_Query_from_Excel_Files3" ref="A1:E5" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:E5" xr:uid="{ABC29F28-E7B5-4281-A032-714C1CF765FF}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{40199137-8C05-41DC-A51A-40FF0DA1317D}" uniqueName="1" name="MSSV" queryTableFieldId="1"/>
+    <tableColumn id="2" xr3:uid="{62254A33-F21B-4589-AB3D-E3F1C1C5A907}" uniqueName="2" name="Hoten" queryTableFieldId="2"/>
+    <tableColumn id="3" xr3:uid="{57C3A876-D8D0-4009-851A-12DA99DF269A}" uniqueName="3" name="F3" queryTableFieldId="3"/>
+    <tableColumn id="4" xr3:uid="{4A912BFC-4470-46D9-B3DE-DD2F067A1C12}" uniqueName="4" name="Lop" queryTableFieldId="4"/>
+    <tableColumn id="5" xr3:uid="{F32A41A8-2CD5-4C8C-808B-84969623B91F}" uniqueName="5" name="MaMH" queryTableFieldId="5"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9C4E5CE6-4797-4E5D-9868-6CBA840014DC}" name="Table_Query_from_Excel_Files4" displayName="Table_Query_from_Excel_Files4" ref="A1:E2" tableType="queryTable" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:E2" xr:uid="{9C4E5CE6-4797-4E5D-9868-6CBA840014DC}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{40E3270F-39D7-4BF9-ADEF-BCC6A70DECC8}" uniqueName="1" name="MSSV" queryTableFieldId="1" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{BF09B982-4DC2-4FA1-9556-0CB895FEE149}" uniqueName="2" name="Hoten" queryTableFieldId="2" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{BEF57A66-0594-4800-8108-7824B1522393}" uniqueName="3" name="F3" queryTableFieldId="3" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{9046878B-4120-48BB-B832-C99F5F36BE9D}" uniqueName="4" name="Lop" queryTableFieldId="4" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{D7DF57B6-B881-48F2-95B7-4C64980D2F2E}" uniqueName="5" name="MaMH" queryTableFieldId="5" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D52749FE-EFF5-4263-9697-4364DBE06D78}" name="Table_Query_from_Excel_Files5" displayName="Table_Query_from_Excel_Files5" ref="A1:F2" tableType="queryTable" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:F2" xr:uid="{D52749FE-EFF5-4263-9697-4364DBE06D78}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{2CBDED2B-6337-4F51-BBCA-4C6F3F37DCEF}" uniqueName="1" name="MSSV" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{683AC8E8-F240-4ADB-B00F-6A52BA585D90}" uniqueName="2" name="Hoten" queryTableFieldId="2" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{DA30E5AE-2544-48C7-947A-8AF6662364D0}" uniqueName="3" name="F3" queryTableFieldId="3" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{3A0E4101-D2E2-41B9-9F92-017F0F06262A}" uniqueName="4" name="Lop" queryTableFieldId="4" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{D8354723-B20F-4105-BD3F-5EBDA8B5EA29}" uniqueName="5" name="MaMH" queryTableFieldId="5" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{60018809-83A0-489D-967D-0EF0578D75EF}" uniqueName="6" name="Diem" queryTableFieldId="6" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -800,8 +1237,278 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDB32D60-8BDF-4E26-9936-4799DC69CD61}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15" style="19" customWidth="1"/>
+    <col min="2" max="2" width="22" style="19" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" style="19" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" style="19" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6009F087-A0A5-4660-B00D-49A139C6908A}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF918BF8-BC81-4136-B4C0-A26E6673036E}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.5546875" style="19" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="19" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="19" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41568556-4BDE-4012-A340-B338FD36475E}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.21875" style="19" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="19" customWidth="1"/>
+    <col min="3" max="4" width="11.6640625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="9" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{441929FB-104C-4050-98FF-5F0F6E2C3A39}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -810,342 +1517,221 @@
     <col min="4" max="4" width="15.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="21" t="s">
+      <c r="C1" s="15"/>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+    </row>
+    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="8">
         <v>1111434</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="22" t="str">
-        <f>VLOOKUP(A2,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT447</v>
-      </c>
-      <c r="F2" s="22" t="str">
-        <f>VLOOKUP(A2, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>A</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
+    </row>
+    <row r="3" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="8">
         <v>1111450</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="str">
-        <f>VLOOKUP(A3,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT107</v>
-      </c>
-      <c r="F3" s="22" t="str">
-        <f>VLOOKUP(A3, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>A</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="22" t="str">
-        <f>VLOOKUP(A4,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT178</v>
-      </c>
-      <c r="F4" s="22" t="str">
-        <f>VLOOKUP(A4, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>C</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="22" t="str">
-        <f>VLOOKUP(A5,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT447</v>
-      </c>
-      <c r="F5" s="22" t="str">
-        <f>VLOOKUP(A5, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>D</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="22" t="str">
-        <f>VLOOKUP(A6,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT107</v>
-      </c>
-      <c r="F6" s="22" t="str">
-        <f>VLOOKUP(A6, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="22" t="str">
-        <f>VLOOKUP(A7,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT178</v>
-      </c>
-      <c r="F7" s="22" t="str">
-        <f>VLOOKUP(A7, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="22" t="str">
-        <f>VLOOKUP(A8,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT447</v>
-      </c>
-      <c r="F8" s="22" t="str">
-        <f>VLOOKUP(A8, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>A</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="22" t="str">
-        <f>VLOOKUP(A9,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT107</v>
-      </c>
-      <c r="F9" s="22" t="str">
-        <f>VLOOKUP(A9, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>C</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="22" t="str">
-        <f>VLOOKUP(A10,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT178</v>
-      </c>
-      <c r="F10" s="22" t="str">
-        <f>VLOOKUP(A10, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>D</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="22" t="str">
-        <f>VLOOKUP(A11,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT447</v>
-      </c>
-      <c r="F11" s="22" t="str">
-        <f>VLOOKUP(A11, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
+    </row>
+    <row r="12" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="22" t="str">
-        <f>VLOOKUP(A12,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT107</v>
-      </c>
-      <c r="F12" s="22" t="str">
-        <f>VLOOKUP(A12, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E13" s="22" t="str">
-        <f>VLOOKUP(A13,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT178</v>
-      </c>
-      <c r="F13" s="22" t="str">
-        <f>VLOOKUP(A13, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="22" t="str">
-        <f>VLOOKUP(A14,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT447</v>
-      </c>
-      <c r="F14" s="22" t="str">
-        <f>VLOOKUP(A14, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>C</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E15" s="22" t="str">
-        <f>VLOOKUP(A15,Sheet2!$A$2:$B$15, 2, FALSE)</f>
-        <v>CT107</v>
-      </c>
-      <c r="F15" s="22" t="str">
-        <f>VLOOKUP(A15, Sheet2!$A$2:$C$100, 3, FALSE)</f>
-        <v>D</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+    </row>
+    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15" xr:uid="{441929FB-104C-4050-98FF-5F0F6E2C3A39}">
-    <filterColumn colId="1" showButton="0"/>
-  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
@@ -1153,9 +1739,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527BC61D-349A-4ABF-ADC4-AAE864D1F6A3}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -1164,416 +1750,227 @@
     <col min="4" max="4" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
         <v>1111434</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="20" t="str">
-        <f>VLOOKUP(B2,Sheet3!$A$2:$C$4, 2, FALSE)</f>
-        <v>Quan Tri He Thong</v>
-      </c>
-      <c r="E2" s="20">
-        <f>VLOOKUP(B2,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="16">
         <v>1111450</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="20" t="str">
-        <f>VLOOKUP(B3,Sheet3!$A$2:$C$4, 2, FALSE)</f>
-        <v>He Dieu Hanh</v>
-      </c>
-      <c r="E3" s="20">
-        <f>VLOOKUP(B3,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="14" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="20" t="str">
-        <f>VLOOKUP(B4, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Nen tang CNTT</v>
-      </c>
-      <c r="E4" s="20">
-        <f>VLOOKUP(B4,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="20" t="str">
-        <f>VLOOKUP(B5, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Quan Tri He Thong</v>
-      </c>
-      <c r="E5" s="20">
-        <f>VLOOKUP(B5,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="14" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="20" t="str">
-        <f>VLOOKUP(B6, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>He Dieu Hanh</v>
-      </c>
-      <c r="E6" s="20">
-        <f>VLOOKUP(B6,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="20" t="str">
-        <f>VLOOKUP(B7, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Nen tang CNTT</v>
-      </c>
-      <c r="E7" s="20">
-        <f>VLOOKUP(B7,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="14" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="20" t="str">
-        <f>VLOOKUP(B8, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Quan Tri He Thong</v>
-      </c>
-      <c r="E8" s="20">
-        <f>VLOOKUP(B8,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="20" t="str">
-        <f>VLOOKUP(B9, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>He Dieu Hanh</v>
-      </c>
-      <c r="E9" s="20">
-        <f>VLOOKUP(B9,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="20" t="str">
-        <f>VLOOKUP(B10, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Nen tang CNTT</v>
-      </c>
-      <c r="E10" s="20">
-        <f>VLOOKUP(B10,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="14" t="s">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="20" t="str">
-        <f>VLOOKUP(B11, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Quan Tri He Thong</v>
-      </c>
-      <c r="E11" s="20">
-        <f>VLOOKUP(B11,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="20" t="str">
-        <f>VLOOKUP(B12, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>He Dieu Hanh</v>
-      </c>
-      <c r="E12" s="20">
-        <f>VLOOKUP(B12,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="14" t="s">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="20" t="str">
-        <f>VLOOKUP(B13, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Nen tang CNTT</v>
-      </c>
-      <c r="E13" s="20">
-        <f>VLOOKUP(B13,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="14" t="s">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="20" t="str">
-        <f>VLOOKUP(B14, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>Quan Tri He Thong</v>
-      </c>
-      <c r="E14" s="20">
-        <f>VLOOKUP(B14,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="20" t="str">
-        <f>VLOOKUP(B15, Sheet3!$A$2:$C$10, 2, FALSE)</f>
-        <v>He Dieu Hanh</v>
-      </c>
-      <c r="E15" s="20">
-        <f>VLOOKUP(B15,Sheet3!$A$2:$C$4, 3, FALSE)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="14"/>
-      <c r="B16" s="12">
-        <f>COUNTIF(Sheet2!B2:B15, "CT447")</f>
-        <v>5</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>60</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{527BC61D-349A-4ABF-ADC4-AAE864D1F6A3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C648238E-20DF-4D80-8DCD-826219411E45}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="11">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="16"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-    </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-    </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="16"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-    </row>
-    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-    </row>
-    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="16"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-    </row>
-    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-    </row>
-    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="16"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-    </row>
-    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-    </row>
-    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="16"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-    </row>
-    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-    </row>
-    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="16"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-    </row>
-    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
